--- a/File tài chính cá nhân/Bảng cân đối thu - chi cá nhân.xlsx
+++ b/File tài chính cá nhân/Bảng cân đối thu - chi cá nhân.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\File tài chính cá nhân\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\BackUp\backup-PC\File tài chính cá nhân\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4C3816-6CAA-4A74-A800-2EBCB0D84A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC72270-871B-4BED-931A-2D05C3EAE1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{01424E0D-5617-48C9-A47B-ABAE5C326979}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{01424E0D-5617-48C9-A47B-ABAE5C326979}"/>
   </bookViews>
   <sheets>
     <sheet name="MẪU" sheetId="1" r:id="rId1"/>
     <sheet name="2026_06_Chi tiết" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026_06_Chi tiết'!$S$1:$S$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026_06_Chi tiết'!$S$1:$S$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="83">
   <si>
     <t>THU NHẬP</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>Bãi xe</t>
+  </si>
+  <si>
+    <t>Mua máy tính mới</t>
+  </si>
+  <si>
+    <t>Sửa máy tính</t>
+  </si>
+  <si>
+    <t>Ăn trứa</t>
   </si>
 </sst>
 </file>
@@ -973,14 +982,14 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="26.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="21.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="30.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1193,29 +1202,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4422289-F014-4091-87C0-8523A89BDE69}">
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="26.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="21.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="30.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20" style="20" customWidth="1"/>
-    <col min="19" max="19" width="21.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2870,43 +2879,79 @@
       <c r="T49" s="10"/>
     </row>
     <row r="50" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J50" s="4"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="10"/>
+      <c r="J50" s="4">
+        <v>46185</v>
+      </c>
+      <c r="K50" s="5">
+        <v>6000</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="Q50" s="2"/>
       <c r="R50" s="19"/>
       <c r="S50" s="3"/>
       <c r="T50" s="10"/>
     </row>
     <row r="51" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J51" s="4"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="10"/>
+      <c r="J51" s="4">
+        <v>46187</v>
+      </c>
+      <c r="K51" s="5">
+        <v>90000</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="Q51" s="2"/>
       <c r="R51" s="19"/>
       <c r="S51" s="3"/>
       <c r="T51" s="10"/>
     </row>
     <row r="52" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J52" s="4"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="10"/>
+      <c r="J52" s="4">
+        <v>46187</v>
+      </c>
+      <c r="K52" s="5">
+        <v>2150</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O52" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="Q52" s="2"/>
       <c r="R52" s="19"/>
       <c r="S52" s="3"/>
       <c r="T52" s="10"/>
     </row>
     <row r="53" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J53" s="2"/>
+      <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="3"/>
       <c r="M53" s="10"/>
@@ -2918,7 +2963,7 @@
       <c r="T53" s="10"/>
     </row>
     <row r="54" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J54" s="2"/>
+      <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="3"/>
       <c r="M54" s="10"/>
@@ -2930,7 +2975,7 @@
       <c r="T54" s="10"/>
     </row>
     <row r="55" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J55" s="2"/>
+      <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="3"/>
       <c r="M55" s="10"/>
@@ -2942,7 +2987,7 @@
       <c r="T55" s="10"/>
     </row>
     <row r="56" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J56" s="2"/>
+      <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="3"/>
       <c r="M56" s="10"/>
@@ -2954,7 +2999,7 @@
       <c r="T56" s="10"/>
     </row>
     <row r="57" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J57" s="2"/>
+      <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="3"/>
       <c r="M57" s="10"/>
@@ -2966,7 +3011,7 @@
       <c r="T57" s="10"/>
     </row>
     <row r="58" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J58" s="2"/>
+      <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="3"/>
       <c r="M58" s="10"/>
@@ -2978,7 +3023,7 @@
       <c r="T58" s="10"/>
     </row>
     <row r="59" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J59" s="2"/>
+      <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="3"/>
       <c r="M59" s="10"/>
@@ -3014,37 +3059,124 @@
       <c r="T61" s="10"/>
     </row>
     <row r="62" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J62" s="16" t="s">
+      <c r="J62" s="2"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="23"/>
+      <c r="O62" s="10"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="19"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="10"/>
+    </row>
+    <row r="63" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J63" s="2"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="23"/>
+      <c r="O63" s="10"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="19"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="10"/>
+    </row>
+    <row r="64" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J64" s="2"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="23"/>
+      <c r="O64" s="10"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="10"/>
+    </row>
+    <row r="65" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J65" s="2"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="23"/>
+      <c r="O65" s="10"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="19"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="10"/>
+    </row>
+    <row r="66" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J66" s="2"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="23"/>
+      <c r="O66" s="10"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="19"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="10"/>
+    </row>
+    <row r="67" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J67" s="2"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="23"/>
+      <c r="O67" s="10"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="19"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="10"/>
+    </row>
+    <row r="68" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J68" s="2"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="10"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="19"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="10"/>
+    </row>
+    <row r="69" spans="10:20" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J69" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="K62" s="31">
-        <f>SUM(K3:K61)</f>
-        <v>292380.69549150026</v>
-      </c>
-      <c r="L62" s="32"/>
-      <c r="M62" s="32"/>
-      <c r="N62" s="32"/>
-      <c r="O62" s="33"/>
-      <c r="Q62" s="16" t="s">
+      <c r="K69" s="31">
+        <f>SUM(K3:K68)</f>
+        <v>390530.69549150026</v>
+      </c>
+      <c r="L69" s="32"/>
+      <c r="M69" s="32"/>
+      <c r="N69" s="32"/>
+      <c r="O69" s="33"/>
+      <c r="Q69" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="R62" s="27">
-        <f>SUM(R3:R61)</f>
+      <c r="R69" s="27">
+        <f>SUM(R3:R68)</f>
         <v>321009000</v>
       </c>
-      <c r="S62" s="28"/>
-      <c r="T62" s="29"/>
+      <c r="S69" s="28"/>
+      <c r="T69" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="S1:S62" xr:uid="{E4422289-F014-4091-87C0-8523A89BDE69}"/>
+  <autoFilter ref="S1:S69" xr:uid="{E4422289-F014-4091-87C0-8523A89BDE69}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J3:O57">
+    <sortCondition ref="J3:J57"/>
+  </sortState>
   <mergeCells count="7">
     <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="R69:T69"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:O1"/>
-    <mergeCell ref="K62:O62"/>
+    <mergeCell ref="K69:O69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
